--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Vendor_Contact_List.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Vendor_Contact_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,7 +746,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rocky Mountain Racking</t>
+          <t>Owen Pike Hauling</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -754,7 +754,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>88 Gold Ave Billings MT 59101</t>
+          <t>PO Box 412 Bozeman MT 59771</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -762,84 +762,100 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summit Tire Import</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(208) 555-0199 </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ar@summittire.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Raj  Patel</t>
-        </is>
-      </c>
+          <t>Rocky Mountain Racking</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18 Harbor Rd Boise ID 83702</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ST-4410</t>
-        </is>
-      </c>
+          <t>88 Gold Ave Billings MT 59101</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tri-County Tool Rental</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>Summit Tire Import</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(208) 555-0199 </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ar@summittire.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Raj  Patel</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77 Frontage Rd Belgrade MT 59714</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>18 Harbor Rd Boise ID 83702</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ST-4410</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Velo Freight Lines</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(406) 555-0177 </t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ops@velofreight.com</t>
-        </is>
-      </c>
+          <t>Tri-County Tool Rental</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
+          <t>77 Frontage Rd Belgrade MT 59714</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(406) 555-0177 </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ops@velofreight.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>900 Frontage Rd Belgrade MT 59714</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>VF-331</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve"> Wednesday, July 15, 2026 10:50 AM GMTZ</t>
         </is>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Vendor_Contact_List.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Vendor_Contact_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,63 +574,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Granite Peak Properties</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(406) 555-0110 </t>
-        </is>
-      </c>
+          <t>Gallatin Display Works</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tom  Beck</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12 Main St Bozeman MT 59715</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UNIT-4</t>
-        </is>
-      </c>
+          <t>PO Box 88 Belgrade MT 59714</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hyalite Fabrication</t>
+          <t>Granite Peak Properties</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone:(406) 555-0121 </t>
+          <t xml:space="preserve">Phone:(406) 555-0110 </t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tom  Beck</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15 Rouse Ave Bozeman MT 59715</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>12 Main St Bozeman MT 59715</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UNIT-4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Idaho State Tax Commission</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Hyalite Fabrication</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(406) 555-0121 </t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PO Box 36 Boise ID 83722</t>
+          <t>15 Rouse Ave Bozeman MT 59715</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -638,71 +638,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kinetic Drivetrain Co.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(303) 555-0167 </t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>billing@kineticdt.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Maria  Lund</t>
-        </is>
-      </c>
+          <t>Idaho State Tax Commission</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5500 Brighton Blvd Denver CO 80216</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KD-2093</t>
-        </is>
-      </c>
+          <t>PO Box 36 Boise ID 83722</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Moraine Cycle Components</t>
+          <t>Kinetic Drivetrain Co.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone:(406) 555-0142 </t>
+          <t xml:space="preserve">Phone:(303) 555-0167 </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>orders@morainecycle.com</t>
+          <t>billing@kineticdt.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lena  Voss</t>
+          <t>Maria  Lund</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>220 Industrial Way Missoula MT 59808</t>
+          <t>5500 Brighton Blvd Denver CO 80216</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC-7781</t>
+          <t>KD-2093</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Moraine Cycle Components, Inc.</t>
+          <t>Moraine Cycle Components</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -710,59 +694,75 @@
           <t xml:space="preserve">Phone:(406) 555-0142 </t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>orders@morainecycle.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lena  Voss</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>220 Industrial Way Missoula MT 59808</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MC-7781</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Northwestern Energy</t>
+          <t>Moraine Cycle Components, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone:(888) 555-0100 </t>
+          <t xml:space="preserve">Phone:(406) 555-0142 </t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PO Box 9 Butte MT 59701</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>556120</t>
-        </is>
-      </c>
+          <t>220 Industrial Way Missoula MT 59808</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Owen Pike Hauling</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Northwestern Energy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(888) 555-0100 </t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PO Box 412 Bozeman MT 59771</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>PO Box 9 Butte MT 59701</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>556120</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rocky Mountain Racking</t>
+          <t>Owen Pike Hauling</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -770,7 +770,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>88 Gold Ave Billings MT 59101</t>
+          <t>PO Box 412 Bozeman MT 59771</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -778,84 +778,100 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summit Tire Import</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(208) 555-0199 </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ar@summittire.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Raj  Patel</t>
-        </is>
-      </c>
+          <t>Rocky Mountain Racking</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18 Harbor Rd Boise ID 83702</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ST-4410</t>
-        </is>
-      </c>
+          <t>88 Gold Ave Billings MT 59101</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tri-County Tool Rental</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>Summit Tire Import</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(208) 555-0199 </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ar@summittire.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Raj  Patel</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77 Frontage Rd Belgrade MT 59714</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>18 Harbor Rd Boise ID 83702</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ST-4410</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Velo Freight Lines</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phone:(406) 555-0177 </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ops@velofreight.com</t>
-        </is>
-      </c>
+          <t>Tri-County Tool Rental</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
+          <t>77 Frontage Rd Belgrade MT 59714</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone:(406) 555-0177 </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ops@velofreight.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>900 Frontage Rd Belgrade MT 59714</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>VF-331</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23"/>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t xml:space="preserve"> Wednesday, July 15, 2026 10:50 AM GMTZ</t>
         </is>
